--- a/output/yearly_total_coral_cover_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_57_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250193296777139</v>
+        <v>1.303374569916189</v>
       </c>
       <c r="C3" t="n">
-        <v>4.610176172712603</v>
+        <v>4.628750839276953</v>
       </c>
       <c r="D3" t="n">
-        <v>6.184544300530029</v>
+        <v>6.071947656329962</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04491377001977</v>
+        <v>12.0040730655231</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.374476038788815</v>
+        <v>1.502522572034156</v>
       </c>
       <c r="C4" t="n">
-        <v>5.063488634457446</v>
+        <v>5.129645977133469</v>
       </c>
       <c r="D4" t="n">
-        <v>6.463634554229773</v>
+        <v>6.356742687445201</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90159922747603</v>
+        <v>12.98891123661283</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.543602218099019</v>
+        <v>1.757349601206764</v>
       </c>
       <c r="C5" t="n">
-        <v>5.657308366674309</v>
+        <v>5.796580513856672</v>
       </c>
       <c r="D5" t="n">
-        <v>6.92305648855873</v>
+        <v>6.638259498183687</v>
       </c>
       <c r="E5" t="n">
-        <v>14.12396707333206</v>
+        <v>14.19218961324712</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.74624248477114</v>
+        <v>2.051759441139635</v>
       </c>
       <c r="C6" t="n">
-        <v>6.407826752012311</v>
+        <v>6.632116635905228</v>
       </c>
       <c r="D6" t="n">
-        <v>7.478209843503809</v>
+        <v>7.046029045580521</v>
       </c>
       <c r="E6" t="n">
-        <v>15.63227908028726</v>
+        <v>15.72990512262538</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.97303187043202</v>
+        <v>2.386038868233582</v>
       </c>
       <c r="C7" t="n">
-        <v>7.331526602402326</v>
+        <v>7.605384650791007</v>
       </c>
       <c r="D7" t="n">
-        <v>7.950400306585283</v>
+        <v>7.508864340285633</v>
       </c>
       <c r="E7" t="n">
-        <v>17.25495877941963</v>
+        <v>17.50028785931022</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.222846524970499</v>
+        <v>1.556527103630497</v>
       </c>
       <c r="C8" t="n">
-        <v>5.069552865032746</v>
+        <v>5.236975023686353</v>
       </c>
       <c r="D8" t="n">
-        <v>6.224514372201259</v>
+        <v>5.827346035297562</v>
       </c>
       <c r="E8" t="n">
-        <v>12.5169137622045</v>
+        <v>12.62084816261441</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.550784209932755</v>
+        <v>1.998121472164436</v>
       </c>
       <c r="C9" t="n">
-        <v>6.311441661264991</v>
+        <v>6.335094598949825</v>
       </c>
       <c r="D9" t="n">
-        <v>6.830614570557457</v>
+        <v>6.34679506191352</v>
       </c>
       <c r="E9" t="n">
-        <v>14.6928404417552</v>
+        <v>14.68001113302778</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.89104809541579</v>
+        <v>2.459376117624314</v>
       </c>
       <c r="C10" t="n">
-        <v>7.737831008809589</v>
+        <v>7.532326091694403</v>
       </c>
       <c r="D10" t="n">
-        <v>7.435180385509212</v>
+        <v>6.858521319419782</v>
       </c>
       <c r="E10" t="n">
-        <v>17.06405948973459</v>
+        <v>16.8502235287385</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.232333845241611</v>
+        <v>2.92059867670883</v>
       </c>
       <c r="C11" t="n">
-        <v>9.318681536330518</v>
+        <v>8.794875896552131</v>
       </c>
       <c r="D11" t="n">
-        <v>8.020551412371084</v>
+        <v>7.381503165173657</v>
       </c>
       <c r="E11" t="n">
-        <v>19.57156679394321</v>
+        <v>19.09697773843462</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.570863294745945</v>
+        <v>3.381420944052434</v>
       </c>
       <c r="C12" t="n">
-        <v>10.97463169764873</v>
+        <v>10.11862941979377</v>
       </c>
       <c r="D12" t="n">
-        <v>8.681820583612389</v>
+        <v>7.938056521317021</v>
       </c>
       <c r="E12" t="n">
-        <v>22.22731557600706</v>
+        <v>21.43810688516322</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.902750309320938</v>
+        <v>3.812541757086739</v>
       </c>
       <c r="C13" t="n">
-        <v>12.59841192306961</v>
+        <v>11.45345316890569</v>
       </c>
       <c r="D13" t="n">
-        <v>9.360227050109799</v>
+        <v>8.398745022540474</v>
       </c>
       <c r="E13" t="n">
-        <v>24.86138928250034</v>
+        <v>23.66473994853291</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.660361169853333</v>
+        <v>2.180726723012313</v>
       </c>
       <c r="C14" t="n">
-        <v>8.714611123948364</v>
+        <v>8.100282498015924</v>
       </c>
       <c r="D14" t="n">
-        <v>7.057951142940041</v>
+        <v>6.370060161528387</v>
       </c>
       <c r="E14" t="n">
-        <v>17.43292343674174</v>
+        <v>16.65106938255662</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.712963211846877</v>
+        <v>2.248781473870701</v>
       </c>
       <c r="C15" t="n">
-        <v>9.468711170534426</v>
+        <v>8.564227010611837</v>
       </c>
       <c r="D15" t="n">
-        <v>7.159218418633101</v>
+        <v>6.385424513099849</v>
       </c>
       <c r="E15" t="n">
-        <v>18.34089280101441</v>
+        <v>17.19843299758239</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.988529974951915</v>
+        <v>2.631810340682595</v>
       </c>
       <c r="C16" t="n">
-        <v>11.18446254586136</v>
+        <v>9.9747432072114</v>
       </c>
       <c r="D16" t="n">
-        <v>7.756768976299965</v>
+        <v>6.851126354086365</v>
       </c>
       <c r="E16" t="n">
-        <v>20.92976149711324</v>
+        <v>19.45767990198036</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.601446490121482</v>
+        <v>2.118876617644764</v>
       </c>
       <c r="C17" t="n">
-        <v>10.31940537374133</v>
+        <v>9.067402161469456</v>
       </c>
       <c r="D17" t="n">
-        <v>7.283429138174407</v>
+        <v>6.358681705636166</v>
       </c>
       <c r="E17" t="n">
-        <v>19.20428100203722</v>
+        <v>17.54496048475039</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.817372080193526</v>
+        <v>2.43863184491795</v>
       </c>
       <c r="C18" t="n">
-        <v>12.0414301168984</v>
+        <v>10.46769836446781</v>
       </c>
       <c r="D18" t="n">
-        <v>7.802115902759125</v>
+        <v>6.820898342272607</v>
       </c>
       <c r="E18" t="n">
-        <v>21.66091809985105</v>
+        <v>19.72722855165836</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.811039807501134</v>
+        <v>2.471618567780643</v>
       </c>
       <c r="C19" t="n">
-        <v>12.89456887188888</v>
+        <v>11.10004206077318</v>
       </c>
       <c r="D19" t="n">
-        <v>7.945451067579158</v>
+        <v>6.938953503708286</v>
       </c>
       <c r="E19" t="n">
-        <v>22.65105974696917</v>
+        <v>20.51061413226211</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.99928992979046</v>
+        <v>2.789704823956609</v>
       </c>
       <c r="C20" t="n">
-        <v>14.81867656248812</v>
+        <v>12.67137834880541</v>
       </c>
       <c r="D20" t="n">
-        <v>8.485942448675198</v>
+        <v>7.439556475580776</v>
       </c>
       <c r="E20" t="n">
-        <v>25.30390894095378</v>
+        <v>22.9006396483428</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.177979435371663</v>
+        <v>1.681341118293088</v>
       </c>
       <c r="C21" t="n">
-        <v>10.86839868995614</v>
+        <v>9.303286682368837</v>
       </c>
       <c r="D21" t="n">
-        <v>7.121961093256934</v>
+        <v>6.218468498515636</v>
       </c>
       <c r="E21" t="n">
-        <v>19.16833921858474</v>
+        <v>17.20309629917756</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_57_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.303374569916189</v>
+        <v>1.280470395976111</v>
       </c>
       <c r="C3" t="n">
-        <v>4.628750839276953</v>
+        <v>4.605571775979685</v>
       </c>
       <c r="D3" t="n">
-        <v>6.071947656329962</v>
+        <v>6.058320998195016</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0040730655231</v>
+        <v>11.94436317015081</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.502522572034156</v>
+        <v>1.45436828243256</v>
       </c>
       <c r="C4" t="n">
-        <v>5.129645977133469</v>
+        <v>5.063873469823663</v>
       </c>
       <c r="D4" t="n">
-        <v>6.356742687445201</v>
+        <v>6.384841512948834</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98891123661283</v>
+        <v>12.90308326520506</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.757349601206764</v>
+        <v>1.688773102230529</v>
       </c>
       <c r="C5" t="n">
-        <v>5.796580513856672</v>
+        <v>5.644899795140615</v>
       </c>
       <c r="D5" t="n">
-        <v>6.638259498183687</v>
+        <v>6.710423855624044</v>
       </c>
       <c r="E5" t="n">
-        <v>14.19218961324712</v>
+        <v>14.04409675299519</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.051759441139635</v>
+        <v>1.955175435884267</v>
       </c>
       <c r="C6" t="n">
-        <v>6.632116635905228</v>
+        <v>6.340800749352701</v>
       </c>
       <c r="D6" t="n">
-        <v>7.046029045580521</v>
+        <v>7.128326356252658</v>
       </c>
       <c r="E6" t="n">
-        <v>15.72990512262538</v>
+        <v>15.42430254148963</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.386038868233582</v>
+        <v>2.248296884179974</v>
       </c>
       <c r="C7" t="n">
-        <v>7.605384650791007</v>
+        <v>7.147791667121646</v>
       </c>
       <c r="D7" t="n">
-        <v>7.508864340285633</v>
+        <v>7.579924013812256</v>
       </c>
       <c r="E7" t="n">
-        <v>17.50028785931022</v>
+        <v>16.97601256511388</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.556527103630497</v>
+        <v>1.441259133195233</v>
       </c>
       <c r="C8" t="n">
-        <v>5.236975023686353</v>
+        <v>4.791481932487489</v>
       </c>
       <c r="D8" t="n">
-        <v>5.827346035297562</v>
+        <v>5.829172030224644</v>
       </c>
       <c r="E8" t="n">
-        <v>12.62084816261441</v>
+        <v>12.06191309590737</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.998121472164436</v>
+        <v>1.835536495484573</v>
       </c>
       <c r="C9" t="n">
-        <v>6.335094598949825</v>
+        <v>5.823747763068188</v>
       </c>
       <c r="D9" t="n">
-        <v>6.34679506191352</v>
+        <v>6.440761317682261</v>
       </c>
       <c r="E9" t="n">
-        <v>14.68001113302778</v>
+        <v>14.10004557623502</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.459376117624314</v>
+        <v>2.257642249631292</v>
       </c>
       <c r="C10" t="n">
-        <v>7.532326091694403</v>
+        <v>6.981212353424275</v>
       </c>
       <c r="D10" t="n">
-        <v>6.858521319419782</v>
+        <v>7.026177381221857</v>
       </c>
       <c r="E10" t="n">
-        <v>16.8502235287385</v>
+        <v>16.26503198427742</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.92059867670883</v>
+        <v>2.69685583714565</v>
       </c>
       <c r="C11" t="n">
-        <v>8.794875896552131</v>
+        <v>8.24951495605414</v>
       </c>
       <c r="D11" t="n">
-        <v>7.381503165173657</v>
+        <v>7.618179725645605</v>
       </c>
       <c r="E11" t="n">
-        <v>19.09697773843462</v>
+        <v>18.56455051884539</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.381420944052434</v>
+        <v>3.136919886877732</v>
       </c>
       <c r="C12" t="n">
-        <v>10.11862941979377</v>
+        <v>9.595834854286542</v>
       </c>
       <c r="D12" t="n">
-        <v>7.938056521317021</v>
+        <v>8.201555122897695</v>
       </c>
       <c r="E12" t="n">
-        <v>21.43810688516322</v>
+        <v>20.93430986406197</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.812541757086739</v>
+        <v>3.558264467640835</v>
       </c>
       <c r="C13" t="n">
-        <v>11.45345316890569</v>
+        <v>10.98036680553828</v>
       </c>
       <c r="D13" t="n">
-        <v>8.398745022540474</v>
+        <v>8.733791120349807</v>
       </c>
       <c r="E13" t="n">
-        <v>23.66473994853291</v>
+        <v>23.27242239352892</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180726723012313</v>
+        <v>2.045009920377233</v>
       </c>
       <c r="C14" t="n">
-        <v>8.100282498015924</v>
+        <v>7.736201361895993</v>
       </c>
       <c r="D14" t="n">
-        <v>6.370060161528387</v>
+        <v>6.632618767552153</v>
       </c>
       <c r="E14" t="n">
-        <v>16.65106938255662</v>
+        <v>16.41383004982538</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.248781473870701</v>
+        <v>2.113987514077615</v>
       </c>
       <c r="C15" t="n">
-        <v>8.564227010611837</v>
+        <v>8.308982424984709</v>
       </c>
       <c r="D15" t="n">
-        <v>6.385424513099849</v>
+        <v>6.710530265361181</v>
       </c>
       <c r="E15" t="n">
-        <v>17.19843299758239</v>
+        <v>17.13350020442351</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.631810340682595</v>
+        <v>2.484420557844021</v>
       </c>
       <c r="C16" t="n">
-        <v>9.9747432072114</v>
+        <v>9.771933766468095</v>
       </c>
       <c r="D16" t="n">
-        <v>6.851126354086365</v>
+        <v>7.203436335232377</v>
       </c>
       <c r="E16" t="n">
-        <v>19.45767990198036</v>
+        <v>19.45979065954449</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.118876617644764</v>
+        <v>2.010530941004085</v>
       </c>
       <c r="C17" t="n">
-        <v>9.067402161469456</v>
+        <v>9.001379628358858</v>
       </c>
       <c r="D17" t="n">
-        <v>6.358681705636166</v>
+        <v>6.714957947507333</v>
       </c>
       <c r="E17" t="n">
-        <v>17.54496048475039</v>
+        <v>17.72686851687028</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.43863184491795</v>
+        <v>2.31373390198367</v>
       </c>
       <c r="C18" t="n">
-        <v>10.46769836446781</v>
+        <v>10.43625298550078</v>
       </c>
       <c r="D18" t="n">
-        <v>6.820898342272607</v>
+        <v>7.212576406358914</v>
       </c>
       <c r="E18" t="n">
-        <v>19.72722855165836</v>
+        <v>19.96256329384337</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.471618567780643</v>
+        <v>2.341674441646535</v>
       </c>
       <c r="C19" t="n">
-        <v>11.10004206077318</v>
+        <v>11.09481916298659</v>
       </c>
       <c r="D19" t="n">
-        <v>6.938953503708286</v>
+        <v>7.356588977094879</v>
       </c>
       <c r="E19" t="n">
-        <v>20.51061413226211</v>
+        <v>20.793082581728</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.789704823956609</v>
+        <v>2.629768305457761</v>
       </c>
       <c r="C20" t="n">
-        <v>12.67137834880541</v>
+        <v>12.74439092557025</v>
       </c>
       <c r="D20" t="n">
-        <v>7.439556475580776</v>
+        <v>7.837674804606944</v>
       </c>
       <c r="E20" t="n">
-        <v>22.9006396483428</v>
+        <v>23.21183403563495</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.681341118293088</v>
+        <v>1.572396575552819</v>
       </c>
       <c r="C21" t="n">
-        <v>9.303286682368837</v>
+        <v>9.378930342981056</v>
       </c>
       <c r="D21" t="n">
-        <v>6.218468498515636</v>
+        <v>6.557367806021634</v>
       </c>
       <c r="E21" t="n">
-        <v>17.20309629917756</v>
+        <v>17.50869472455551</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_57_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.280470395976111</v>
+        <v>2.594415092511364</v>
       </c>
       <c r="C3" t="n">
-        <v>4.605571775979685</v>
+        <v>7.738574360696776</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058320998195016</v>
+        <v>8.179350263173383</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94436317015081</v>
+        <v>18.51233971638152</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.45436828243256</v>
+        <v>1.07607258290978</v>
       </c>
       <c r="C4" t="n">
-        <v>5.063873469823663</v>
+        <v>4.555586658632636</v>
       </c>
       <c r="D4" t="n">
-        <v>6.384841512948834</v>
+        <v>5.829234890162167</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90308326520506</v>
+        <v>11.46089413170458</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.688773102230529</v>
+        <v>1.16964820341362</v>
       </c>
       <c r="C5" t="n">
-        <v>5.644899795140615</v>
+        <v>5.235193117841904</v>
       </c>
       <c r="D5" t="n">
-        <v>6.710423855624044</v>
+        <v>6.170382366233686</v>
       </c>
       <c r="E5" t="n">
-        <v>14.04409675299519</v>
+        <v>12.57522368748921</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.955175435884267</v>
+        <v>1.267746739941098</v>
       </c>
       <c r="C6" t="n">
-        <v>6.340800749352701</v>
+        <v>6.079892623696915</v>
       </c>
       <c r="D6" t="n">
-        <v>7.128326356252658</v>
+        <v>6.575956581217066</v>
       </c>
       <c r="E6" t="n">
-        <v>15.42430254148963</v>
+        <v>13.92359594485508</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.248296884179974</v>
+        <v>1.366467875185245</v>
       </c>
       <c r="C7" t="n">
-        <v>7.147791667121646</v>
+        <v>7.105420041632056</v>
       </c>
       <c r="D7" t="n">
-        <v>7.579924013812256</v>
+        <v>7.008007621694256</v>
       </c>
       <c r="E7" t="n">
-        <v>16.97601256511388</v>
+        <v>15.47989553851156</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.441259133195233</v>
+        <v>1.488494811012886</v>
       </c>
       <c r="C8" t="n">
-        <v>4.791481932487489</v>
+        <v>8.297351861306241</v>
       </c>
       <c r="D8" t="n">
-        <v>5.829172030224644</v>
+        <v>7.489151513796315</v>
       </c>
       <c r="E8" t="n">
-        <v>12.06191309590737</v>
+        <v>17.27499818611544</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.835536495484573</v>
+        <v>1.603152048341918</v>
       </c>
       <c r="C9" t="n">
-        <v>5.823747763068188</v>
+        <v>9.622836061526552</v>
       </c>
       <c r="D9" t="n">
-        <v>6.440761317682261</v>
+        <v>8.032315299615432</v>
       </c>
       <c r="E9" t="n">
-        <v>14.10004557623502</v>
+        <v>19.2583034094839</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.257642249631292</v>
+        <v>1.018386528569301</v>
       </c>
       <c r="C10" t="n">
-        <v>6.981212353424275</v>
+        <v>7.099380896059258</v>
       </c>
       <c r="D10" t="n">
-        <v>7.026177381221857</v>
+        <v>6.342374876268626</v>
       </c>
       <c r="E10" t="n">
-        <v>16.26503198427742</v>
+        <v>14.46014230089719</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.69685583714565</v>
+        <v>0.9513626128003716</v>
       </c>
       <c r="C11" t="n">
-        <v>8.24951495605414</v>
+        <v>7.599875875684281</v>
       </c>
       <c r="D11" t="n">
-        <v>7.618179725645605</v>
+        <v>6.276322890726902</v>
       </c>
       <c r="E11" t="n">
-        <v>18.56455051884539</v>
+        <v>14.82756137921155</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.136919886877732</v>
+        <v>1.020860532784003</v>
       </c>
       <c r="C12" t="n">
-        <v>9.595834854286542</v>
+        <v>9.007603908803782</v>
       </c>
       <c r="D12" t="n">
-        <v>8.201555122897695</v>
+        <v>6.759460570940841</v>
       </c>
       <c r="E12" t="n">
-        <v>20.93430986406197</v>
+        <v>16.78792501252862</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.558264467640835</v>
+        <v>0.80334451143108</v>
       </c>
       <c r="C13" t="n">
-        <v>10.98036680553828</v>
+        <v>8.557168244618303</v>
       </c>
       <c r="D13" t="n">
-        <v>8.733791120349807</v>
+        <v>6.241294132639375</v>
       </c>
       <c r="E13" t="n">
-        <v>23.27242239352892</v>
+        <v>15.60180688868876</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.045009920377233</v>
+        <v>0.8604135054789471</v>
       </c>
       <c r="C14" t="n">
-        <v>7.736201361895993</v>
+        <v>9.983677111320048</v>
       </c>
       <c r="D14" t="n">
-        <v>6.632618767552153</v>
+        <v>6.664289948491155</v>
       </c>
       <c r="E14" t="n">
-        <v>16.41383004982538</v>
+        <v>17.50838056529015</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.113987514077615</v>
+        <v>0.8284576177057134</v>
       </c>
       <c r="C15" t="n">
-        <v>8.308982424984709</v>
+        <v>10.74327494504989</v>
       </c>
       <c r="D15" t="n">
-        <v>6.710530265361181</v>
+        <v>6.771074646282081</v>
       </c>
       <c r="E15" t="n">
-        <v>17.13350020442351</v>
+        <v>18.34280720903768</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.484420557844021</v>
+        <v>0.9092063663800136</v>
       </c>
       <c r="C16" t="n">
-        <v>9.771933766468095</v>
+        <v>12.44520331270103</v>
       </c>
       <c r="D16" t="n">
-        <v>7.203436335232377</v>
+        <v>7.234322118007981</v>
       </c>
       <c r="E16" t="n">
-        <v>19.45979065954449</v>
+        <v>20.58873179708903</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.010530941004085</v>
+        <v>0.5483060928218436</v>
       </c>
       <c r="C17" t="n">
-        <v>9.001379628358858</v>
+        <v>9.238785858199821</v>
       </c>
       <c r="D17" t="n">
-        <v>6.714957947507333</v>
+        <v>6.050815443061409</v>
       </c>
       <c r="E17" t="n">
-        <v>17.72686851687028</v>
+        <v>15.83790739408307</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.31373390198367</v>
+        <v>0.436632291463769</v>
       </c>
       <c r="C18" t="n">
-        <v>10.43625298550078</v>
+        <v>8.104759267547289</v>
       </c>
       <c r="D18" t="n">
-        <v>7.212576406358914</v>
+        <v>5.580195046076615</v>
       </c>
       <c r="E18" t="n">
-        <v>19.96256329384337</v>
+        <v>14.12158660508767</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.341674441646535</v>
+        <v>0.5164974672042471</v>
       </c>
       <c r="C19" t="n">
-        <v>11.09481916298659</v>
+        <v>9.935512568949699</v>
       </c>
       <c r="D19" t="n">
-        <v>7.356588977094879</v>
+        <v>6.161085345202411</v>
       </c>
       <c r="E19" t="n">
-        <v>20.793082581728</v>
+        <v>16.61309538135636</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.629768305457761</v>
+        <v>0.5904034343799469</v>
       </c>
       <c r="C20" t="n">
-        <v>12.74439092557025</v>
+        <v>11.86191754917687</v>
       </c>
       <c r="D20" t="n">
-        <v>7.837674804606944</v>
+        <v>6.704963755878102</v>
       </c>
       <c r="E20" t="n">
-        <v>23.21183403563495</v>
+        <v>19.15728473943492</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.572396575552819</v>
+        <v>0.6541384953396497</v>
       </c>
       <c r="C21" t="n">
-        <v>9.378930342981056</v>
+        <v>13.7997304377274</v>
       </c>
       <c r="D21" t="n">
-        <v>6.557367806021634</v>
+        <v>7.183850468532652</v>
       </c>
       <c r="E21" t="n">
-        <v>17.50869472455551</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
   </sheetData>
